--- a/data/trans_dic/IP38F_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP38F_2023-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto que aporta más ingresos al hogar que ha trabajado anteriormente</t>
+          <t>Adulto que aporta más ingresos al hogar que ha trabajado anteriormente (tasa de respuesta: 99,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>41,86; 100,0</t>
+          <t>43,33; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>47,88; 100,0</t>
+          <t>49,82; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61,39; 100,0</t>
+          <t>64,1; 100,0</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>53,15; 100,0</t>
+          <t>63,74; 100,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>83,39; 100,0</t>
+          <t>79,5; 100,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85,75; 100,0</t>
+          <t>82,07; 100,0</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>74,01; 100,0</t>
+          <t>74,07; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85,49; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>81,96; 100,0</t>
+          <t>80,55; 100,0</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>64,43; 95,85</t>
+          <t>65,31; 95,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>72,82; 100,0</t>
+          <t>78,64; 100,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78,86; 96,36</t>
+          <t>78,32; 96,44</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>79,72; 95,55</t>
+          <t>78,94; 95,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>86,56; 99,12</t>
+          <t>87,44; 99,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>87,33; 96,29</t>
+          <t>86,76; 96,7</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adulto que aporta más ingresos al hogar que ha trabajado anteriormente (tasa de respuesta: 99,23%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3314</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6395</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1528; 3526</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1848; 3710</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4639; 7236</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>5970</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11872</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>17842</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>4119; 6462</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>9741; 12253</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>15360; 18715</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>14215</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>8461</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>22676</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>11113; 15003</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>18899; 23464</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>14184</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>19040</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>33224</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>11030; 16193</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>15769; 20052</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>28931; 35625</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>37450</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>42688</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>80137</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>33060; 40102</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>38889; 44090</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>74918; 83506</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP38F_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP38F_2023-Edad-trans_dic.xlsx
@@ -572,7 +572,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>43,33; 100,0</t>
+          <t>45,17; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64,1; 100,0</t>
+          <t>60,72; 100,0</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>63,74; 100,0</t>
+          <t>54,59; 100,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>79,5; 100,0</t>
+          <t>84,07; 100,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82,07; 100,0</t>
+          <t>82,7; 100,0</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>74,07; 100,0</t>
+          <t>73,88; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>80,55; 100,0</t>
+          <t>83,97; 100,0</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>65,31; 95,89</t>
+          <t>63,87; 95,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>78,64; 100,0</t>
+          <t>76,07; 100,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78,32; 96,44</t>
+          <t>78,81; 96,32</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>78,94; 95,76</t>
+          <t>79,97; 95,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>87,44; 99,13</t>
+          <t>86,39; 99,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86,76; 96,7</t>
+          <t>87,28; 96,68</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1528; 3526</t>
+          <t>1593; 3526</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4639; 7236</t>
+          <t>4393; 7236</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4119; 6462</t>
+          <t>3528; 6462</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9741; 12253</t>
+          <t>10302; 12253</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15360; 18715</t>
+          <t>15476; 18715</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11113; 15003</t>
+          <t>11084; 15003</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18899; 23464</t>
+          <t>19704; 23464</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11030; 16193</t>
+          <t>10787; 16178</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15769; 20052</t>
+          <t>15254; 20052</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28931; 35625</t>
+          <t>29111; 35579</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>33060; 40102</t>
+          <t>33489; 40057</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>38889; 44090</t>
+          <t>38422; 44091</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>74918; 83506</t>
+          <t>75373; 83490</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP38F_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP38F_2023-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>89,64%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>45,17; 100,0</t>
+          <t>47,0; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>49,82; 100,0</t>
+          <t>42,63; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60,72; 100,0</t>
+          <t>65,44; 100,0</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,58%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>54,59; 100,0</t>
+          <t>83,91; 100,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>84,07; 100,0</t>
+          <t>55,16; 100,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82,7; 100,0</t>
+          <t>86,25; 100,0</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>95,9%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>73,88; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>71,78; 100,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>83,97; 100,0</t>
+          <t>79,02; 100,0</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>90,29%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>63,87; 95,8</t>
+          <t>73,56; 100,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>76,07; 100,0</t>
+          <t>66,05; 96,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78,81; 96,32</t>
+          <t>79,56; 96,52</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,76%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>79,97; 95,65</t>
+          <t>86,01; 99,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>86,39; 99,13</t>
+          <t>79,35; 95,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>87,28; 96,68</t>
+          <t>86,83; 96,34</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3004</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>2681</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6395</t>
+          <t>5686</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1593; 3526</t>
+          <t>1552; 3302</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1848; 3710</t>
+          <t>1296; 3040</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4393; 7236</t>
+          <t>4151; 6343</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>5970</t>
+          <t>10180</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>11872</t>
+          <t>5726</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17842</t>
+          <t>15906</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3528; 6462</t>
+          <t>8805; 10493</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10302; 12253</t>
+          <t>3391; 6148</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15476; 18715</t>
+          <t>14353; 16641</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14215</t>
+          <t>7981</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8461</t>
+          <t>12149</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22676</t>
+          <t>20129</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11084; 15003</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9337; 13009</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19704; 23464</t>
+          <t>16586; 20989</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>14184</t>
+          <t>19105</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>19040</t>
+          <t>14916</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33224</t>
+          <t>34022</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10787; 16178</t>
+          <t>14781; 20093</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15254; 20052</t>
+          <t>11615; 16908</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29111; 35579</t>
+          <t>29978; 36367</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>54</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>37450</t>
+          <t>40269</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>42688</t>
+          <t>35473</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>80137</t>
+          <t>75743</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>33489; 40057</t>
+          <t>36010; 41558</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>38422; 44091</t>
+          <t>31567; 37926</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>75373; 83490</t>
+          <t>70902; 78667</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP38F_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP38F_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Adulto que aporta más ingresos al hogar que ha trabajado anteriormente (tasa de respuesta: 99,23%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>90,96%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>88,19%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>89,64%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>47,0; 100,0</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>42,63; 100,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>65,44; 100,0</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>97,01%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>93,14%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>95,58%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>83,91; 100,0</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>55,16; 100,0</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>86,25; 100,0</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>93,39%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>95,9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>71,78; 100,0</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>79,02; 100,0</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>95,08%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>84,82%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>90,29%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>73,56; 100,0</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>66,05; 96,14</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>79,56; 96,52</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>96,18%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>89,17%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>92,76%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>86,01; 99,26</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>79,35; 95,33</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>86,83; 96,34</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.9096454675729868</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.8819240017891445</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.8963581811413716</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>3004</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2681</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5686</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.4700059963153178</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.4276746646213242</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.6543756774975152</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1552; 3302</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1296; 3040</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>4151; 6343</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.9701351891159057</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.9314370745819806</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.9558377372207921</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>10180</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>5726</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>15906</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.8391373098300177</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.5515766010887266</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.862517393133395</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>8805; 10493</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>3391; 6148</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>14353; 16641</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,47 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.9339117228232722</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.9590404925901809</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>7981</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>12149</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>20129</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="n">
+        <v>0.7177692979440502</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.7901996448601071</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>9337; 13009</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>16586; 20989</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +713,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.9508078800942427</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.8481893462786173</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.9029124217939094</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>19105</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>14916</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>34022</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.7356151298587003</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.6604819919730425</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.7955959111612424</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>14781; 20093</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>11615; 16908</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>29978; 36367</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.9614238996015892</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.9651601687792427</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +768,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.9617813393191524</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.8916626294165131</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.9276177273610036</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>40269</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>35473</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>75743</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.8600731094049333</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.7934873386867402</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.8683373196577306</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>36010; 41558</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>31567; 37926</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>70902; 78667</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.9925680317576339</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.9533162452234279</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.9634319325998786</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +833,445 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adulto que aporta más ingresos al hogar que ha trabajado anteriormente (tasa de respuesta: 99,23%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>3004</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>2681</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>5686</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>1552</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>4151</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>3302</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>3040</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>6343</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>10180</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>5726</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>15906</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>8805</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>3391</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>14353</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>10493</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>6148</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>16641</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>7981</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>12149</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>20129</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr"/>
+      <c r="D14" s="6" t="n">
+        <v>9337</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>16586</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr"/>
+      <c r="D15" s="6" t="n">
+        <v>13009</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>20989</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>19105</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>14916</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>34022</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>14781</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>11615</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>29978</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>20093</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>16908</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>36367</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>40269</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>35473</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>75743</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>36010</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>31567</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>70902</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>41558</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>37926</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>78667</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>